--- a/Assets/Data/Excel/PoolConfig.xlsx
+++ b/Assets/Data/Excel/PoolConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -48,10 +48,16 @@
     <t xml:space="preserve">DisplayName</t>
   </si>
   <si>
+    <t xml:space="preserve">EntityType</t>
+  </si>
+  <si>
     <t xml:space="preserve">InitialSize</t>
   </si>
   <si>
     <t xml:space="preserve">expandIfEmpty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expandRate</t>
   </si>
   <si>
     <t xml:space="preserve">maxSize</t>
@@ -127,6 +133,12 @@
   </si>
   <si>
     <t xml:space="preserve">jidi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nb</t>
   </si>
 </sst>
 </file>
@@ -237,7 +249,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,10 +376,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -380,59 +393,102 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>7</v>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="G4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/PoolConfig.xlsx
+++ b/Assets/Data/Excel/PoolConfig.xlsx
@@ -132,7 +132,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">jidi</t>
+    <t xml:space="preserve">jidi_lv1</t>
   </si>
   <si>
     <t xml:space="preserve">Building</t>
@@ -468,7 +468,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -477,7 +477,7 @@
       <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="4" t="n">
@@ -487,7 +487,7 @@
       <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>3</v>
       </c>
     </row>

--- a/Assets/Data/Excel/PoolConfig.xlsx
+++ b/Assets/Data/Excel/PoolConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
     <r>
       <rPr>
@@ -51,6 +51,9 @@
     <t xml:space="preserve">EntityType</t>
   </si>
   <si>
+    <t xml:space="preserve">isActive</t>
+  </si>
+  <si>
     <t xml:space="preserve">InitialSize</t>
   </si>
   <si>
@@ -139,6 +142,12 @@
   </si>
   <si>
     <t xml:space="preserve">nb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
   </si>
 </sst>
 </file>
@@ -376,11 +385,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -396,7 +405,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -408,39 +417,45 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -448,22 +463,25 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -472,23 +490,199 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Excel/PoolConfig.xlsx
+++ b/Assets/Data/Excel/PoolConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <r>
       <rPr>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicator</t>
   </si>
 </sst>
 </file>
@@ -241,7 +247,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -259,6 +265,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -385,7 +395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
@@ -468,7 +478,8 @@
       <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="E4" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
@@ -495,7 +506,8 @@
       <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="E5" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F5" s="1" t="n">
@@ -522,7 +534,8 @@
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="E6" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -549,7 +562,8 @@
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="E7" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -567,7 +581,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="1"/>
@@ -579,7 +593,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="n">
-        <v>106</v>
+        <v>1111</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
@@ -587,7 +601,8 @@
       <c r="D9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="4" t="b">
+      <c r="E9" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F9" s="1" t="n">
@@ -606,7 +621,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="n">
-        <v>107</v>
+        <v>2222</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>17</v>
@@ -614,7 +629,8 @@
       <c r="D10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="4" t="b">
+      <c r="E10" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F10" s="1" t="n">
@@ -633,7 +649,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="n">
-        <v>108</v>
+        <v>3333</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>17</v>
@@ -641,7 +657,8 @@
       <c r="D11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="4" t="b">
+      <c r="E11" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F11" s="1" t="n">
@@ -668,7 +685,8 @@
       <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="4" t="b">
+      <c r="E12" s="4" t="n">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F12" s="1" t="n">
@@ -683,6 +701,37 @@
       </c>
       <c r="I12" s="1" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="n">
+        <v>9999</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
